--- a/ig/main/ValueSet-JDV-J07-XdsTypeCode-CISIS.xlsx
+++ b/ig/main/ValueSet-JDV-J07-XdsTypeCode-CISIS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="261">
   <si>
     <t>Property</t>
   </si>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -129,7 +129,7 @@
     <t>ATTEST-DROITS-AM</t>
   </si>
   <si>
-    <t>Attestation de droits à l’assurance maladie</t>
+    <t>Attestation de droits à l'assurance maladie</t>
   </si>
   <si>
     <t>AUTORIS-SOINS</t>
@@ -399,6 +399,12 @@
     <t>Note de transfert (dont lettre de liaison à l'entrée en établissement de soins)</t>
   </si>
   <si>
+    <t>28617-9</t>
+  </si>
+  <si>
+    <t>Bilan bucco-dentaire</t>
+  </si>
+  <si>
     <t>28653-4</t>
   </si>
   <si>
@@ -411,6 +417,12 @@
     <t>Mesures de signes vitaux</t>
   </si>
   <si>
+    <t>34120-6</t>
+  </si>
+  <si>
+    <t>Bilan par auxiliaire médical</t>
+  </si>
+  <si>
     <t>34133-9</t>
   </si>
   <si>
@@ -450,7 +462,7 @@
     <t>47420-5</t>
   </si>
   <si>
-    <t>CR de bilan fonctionnel (par auxiliaire médical)</t>
+    <t>CR de bilan fonctionnel</t>
   </si>
   <si>
     <t>51851-4</t>
@@ -519,6 +531,12 @@
     <t>Attestation de consentement</t>
   </si>
   <si>
+    <t>60280-5</t>
+  </si>
+  <si>
+    <t>Fiche de retour du service des urgences</t>
+  </si>
+  <si>
     <t>60568-3</t>
   </si>
   <si>
@@ -528,7 +546,7 @@
     <t>60591-5</t>
   </si>
   <si>
-    <t>Synthèse du dossier médical</t>
+    <t>Synthèse médicale</t>
   </si>
   <si>
     <t>60593-1</t>
@@ -567,6 +585,12 @@
     <t>CR d'acte diagnostique (autre)</t>
   </si>
   <si>
+    <t>78341-5</t>
+  </si>
+  <si>
+    <t>Fiche de transfert vers le service des urgences</t>
+  </si>
+  <si>
     <t>74207-2</t>
   </si>
   <si>
@@ -769,6 +793,12 @@
   </si>
   <si>
     <t>Synthèse Enfant en Maternité</t>
+  </si>
+  <si>
+    <t>89233-1</t>
+  </si>
+  <si>
+    <t>CR de grossesse</t>
   </si>
 </sst>
 </file>
@@ -1356,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1909,18 +1939,50 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>100</v>
+        <v>237</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>100</v>
+        <v>238</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="B70" t="s" s="2">
-        <v>237</v>
+      <c r="B74" t="s" s="2">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -1947,10 +2009,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3">
@@ -1966,7 +2028,7 @@
         <v>101</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -1976,7 +2038,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1993,58 +2055,66 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="B8" t="s" s="2">
-        <v>237</v>
+      <c r="B9" t="s" s="2">
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-JDV-J07-XdsTypeCode-CISIS.xlsx
+++ b/ig/main/ValueSet-JDV-J07-XdsTypeCode-CISIS.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>20240426120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/ValueSet-JDV-J07-XdsTypeCode-CISIS.xlsx
+++ b/ig/main/ValueSet-JDV-J07-XdsTypeCode-CISIS.xlsx
@@ -84,7 +84,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/ig/main/ValueSet-JDV-J07-XdsTypeCode-CISIS.xlsx
+++ b/ig/main/ValueSet-JDV-J07-XdsTypeCode-CISIS.xlsx
@@ -7,10 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE_A05_TypeDocC" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from TRE-A04-Loinc" r:id="rId5" sheetId="3"/>
-    <sheet name="Include from TRE_A12_Nomencla" r:id="rId6" sheetId="4"/>
-    <sheet name="Include from TRE-A04-Loinc 2" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>

--- a/ig/main/ValueSet-JDV-J07-XdsTypeCode-CISIS.xlsx
+++ b/ig/main/ValueSet-JDV-J07-XdsTypeCode-CISIS.xlsx
@@ -10,13 +10,12 @@
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
-    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="263">
   <si>
     <t>Property</t>
   </si>
@@ -39,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240726120000</t>
+    <t>20240927120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-26T12:00:00+01:00</t>
+    <t>2024-09-27T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -420,7 +419,7 @@
     <t>34120-6</t>
   </si>
   <si>
-    <t>Bilan par auxiliaire médical</t>
+    <t>Bilan par professionnel de santé</t>
   </si>
   <si>
     <t>34133-9</t>
@@ -753,7 +752,49 @@
     <t>Test rapide d'orientation diagnostique</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A04-Loinc/FHIR/TRE-A04-Loinc</t>
+    <t>57055-6</t>
+  </si>
+  <si>
+    <t>Synthèse antepartum</t>
+  </si>
+  <si>
+    <t>57057-2</t>
+  </si>
+  <si>
+    <t>Synthèse Salle de Naissance Mère</t>
+  </si>
+  <si>
+    <t>57075-4</t>
+  </si>
+  <si>
+    <t>Synthèse Salle de Naissance Enfant</t>
+  </si>
+  <si>
+    <t>89235-6</t>
+  </si>
+  <si>
+    <t>Synthèse Suites de Couches Mère</t>
+  </si>
+  <si>
+    <t>78489-2</t>
+  </si>
+  <si>
+    <t>Synthèse Enfant en Maternité</t>
+  </si>
+  <si>
+    <t>89233-1</t>
+  </si>
+  <si>
+    <t>CR de grossesse</t>
+  </si>
+  <si>
+    <t>101881-1</t>
+  </si>
+  <si>
+    <t>Carte d'implant</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
   <si>
     <t>E1762</t>
@@ -763,42 +804,6 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A12-NomenclatureASTM/FHIR/TRE-A12-NomenclatureASTM</t>
-  </si>
-  <si>
-    <t>57055-6</t>
-  </si>
-  <si>
-    <t>Synthèse antepartum</t>
-  </si>
-  <si>
-    <t>57057-2</t>
-  </si>
-  <si>
-    <t>Synthèse Salle de Naissance Mère</t>
-  </si>
-  <si>
-    <t>57075-4</t>
-  </si>
-  <si>
-    <t>Synthèse Salle de Naissance Enfant</t>
-  </si>
-  <si>
-    <t>89235-6</t>
-  </si>
-  <si>
-    <t>Synthèse Suites de Couches Mère</t>
-  </si>
-  <si>
-    <t>78489-2</t>
-  </si>
-  <si>
-    <t>Synthèse Enfant en Maternité</t>
-  </si>
-  <si>
-    <t>89233-1</t>
-  </si>
-  <si>
-    <t>CR de grossesse</t>
   </si>
 </sst>
 </file>
@@ -1386,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1971,18 +1976,74 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>100</v>
+        <v>245</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>100</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="B74" t="s" s="2">
-        <v>245</v>
+      <c r="B81" t="s" s="2">
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -2009,10 +2070,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3">
@@ -2028,93 +2089,7 @@
         <v>101</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>248</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>245</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
